--- a/Ecommerce_Sales_ Project.xlsx
+++ b/Ecommerce_Sales_ Project.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91987\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91987\AppData\Roaming\Microsoft\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457D5FB4-E3DC-4F2E-BACF-7D5252FDCA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6CB769-B294-4950-93C1-749BF16B8C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="18775" windowHeight="9931" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="18775" windowHeight="9931" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pvt tables &amp; KPIs" sheetId="51" r:id="rId1"/>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="361">
   <si>
     <t>Product ID</t>
   </si>
@@ -1320,19 +1320,40 @@
     <t>Jul</t>
   </si>
   <si>
+    <t>5.3 ---&gt; Add a drop-down to filter sales by Month (group Order Date in Pivot)</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
     <t>Oct</t>
   </si>
   <si>
-    <t>Jun</t>
-  </si>
-  <si>
-    <t>Aug</t>
-  </si>
-  <si>
-    <t>(Multiple Items)</t>
-  </si>
-  <si>
-    <t>5.3 ---&gt; Add a drop-down to filter sales by Month (group Order Date in Pivot)</t>
+    <t>Dec</t>
   </si>
 </sst>
 </file>
@@ -1855,8 +1876,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFFFFFF"/>
-      <color rgb="FFFFCCFF"/>
+      <color rgb="FF2B4463"/>
+      <color rgb="FF009999"/>
+      <color rgb="FF60943C"/>
+      <color rgb="FFA18313"/>
+      <color rgb="FF008080"/>
+      <color rgb="FF996600"/>
+      <color rgb="FF021244"/>
+      <color rgb="FF010A25"/>
+      <color rgb="FF6D580D"/>
+      <color rgb="FF966708"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1884,7 +1913,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Workforce &amp; sales.xlsx]pvt tables &amp; KPIs!PivotTable6</c:name>
+    <c:name>[Ecommerce_Sales_ Project.xlsx]pvt tables &amp; KPIs!PivotTable6</c:name>
     <c:fmtId val="8"/>
   </c:pivotSource>
   <c:chart>
@@ -1897,7 +1926,7 @@
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="bg1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1907,7 +1936,7 @@
             <a:r>
               <a:rPr lang="en-GB" b="1">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="bg1"/>
                 </a:solidFill>
               </a:rPr>
               <a:t>Region</a:t>
@@ -1915,14 +1944,14 @@
             <a:r>
               <a:rPr lang="en-GB" b="1" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="bg1"/>
                 </a:solidFill>
               </a:rPr>
               <a:t> Sales By Product Category</a:t>
             </a:r>
             <a:endParaRPr lang="en-GB" b="1">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -1930,7 +1959,9 @@
       </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:srgbClr val="60943C"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -1943,7 +1974,7 @@
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -2576,7 +2607,9 @@
         <c:idx val="11"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent6">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -2632,7 +2665,7 @@
         <c:idx val="12"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:srgbClr val="996600"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -2688,7 +2721,7 @@
         <c:idx val="13"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:srgbClr val="008080"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -2744,7 +2777,7 @@
         <c:idx val="14"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:srgbClr val="7030A0"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -2868,7 +2901,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Electronics</c:v>
+                  <c:v>Books</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2885,23 +2918,47 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'pvt tables &amp; KPIs'!$A$9:$A$10</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$A$9:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>Central</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'pvt tables &amp; KPIs'!$B$9:$B$10</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$B$9:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1056</c:v>
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>394</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>464</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>423</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>350</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2921,14 +2978,16 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Fashion</c:v>
+                  <c:v>Electronics</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2938,30 +2997,54 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'pvt tables &amp; KPIs'!$A$9:$A$10</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$A$9:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>Central</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'pvt tables &amp; KPIs'!$C$9:$C$10</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$C$9:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>88</c:v>
+                  <c:v>2662</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>365</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6522</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3938</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1722</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-98B6-4A0B-B378-3F0A0B35E8BF}"/>
+              <c16:uniqueId val="{00000006-E913-446F-AA3D-5C8EE54EC424}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2974,14 +3057,14 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Home</c:v>
+                  <c:v>Fashion</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3"/>
+              <a:srgbClr val="996600"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2991,30 +3074,54 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'pvt tables &amp; KPIs'!$A$9:$A$10</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$A$9:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>Central</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'pvt tables &amp; KPIs'!$D$9:$D$10</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$D$9:$D$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>685</c:v>
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>711</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>788</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1032</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1131</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000D-98B6-4A0B-B378-3F0A0B35E8BF}"/>
+              <c16:uniqueId val="{00000007-E913-446F-AA3D-5C8EE54EC424}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3027,14 +3134,14 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Toys</c:v>
+                  <c:v>Home</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent4"/>
+              <a:srgbClr val="008080"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -3044,30 +3151,131 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'pvt tables &amp; KPIs'!$A$9:$A$10</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$A$9:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>Central</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'pvt tables &amp; KPIs'!$E$9:$E$10</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$E$9:$E$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>291</c:v>
+                  <c:v>2063</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>741</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2131</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000E-98B6-4A0B-B378-3F0A0B35E8BF}"/>
+              <c16:uniqueId val="{0000000B-E913-446F-AA3D-5C8EE54EC424}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'pvt tables &amp; KPIs'!$F$7:$F$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Toys</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'pvt tables &amp; KPIs'!$A$9:$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Central</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>West</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'pvt tables &amp; KPIs'!$F$9:$F$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>437</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1424</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>586</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1021</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-E913-446F-AA3D-5C8EE54EC424}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3193,7 +3401,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -3218,23 +3426,9 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:gradFill>
-      <a:gsLst>
-        <a:gs pos="84000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="19000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="40000"/>
-            <a:lumOff val="60000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:lin ang="5400000" scaled="1"/>
-    </a:gradFill>
+    <a:solidFill>
+      <a:sysClr val="window" lastClr="FFFFFF"/>
+    </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
@@ -3293,20 +3487,20 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Workforce &amp; sales.xlsx]pvt tables &amp; KPIs!PivotTable7</c:name>
+    <c:name>[Ecommerce_Sales_ Project.xlsx]pvt tables &amp; KPIs!PivotTable7</c:name>
     <c:fmtId val="8"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="t" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="bg1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3316,22 +3510,22 @@
             <a:r>
               <a:rPr lang="en-GB" sz="1400" b="1">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="bg1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Order</a:t>
+              <a:t> Order</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-GB" sz="1400" b="1" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="bg1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t> Status  By Region</a:t>
+              <a:t> Status  By Region    </a:t>
             </a:r>
             <a:endParaRPr lang="en-GB" sz="1400" b="1">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -3339,20 +3533,22 @@
       </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:srgbClr val="009999"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
       <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="t" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -3910,23 +4106,47 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'pvt tables &amp; KPIs'!$A$55:$A$56</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$A$55:$A$60</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>Central</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'pvt tables &amp; KPIs'!$B$55:$B$56</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$B$55:$B$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3978,23 +4198,47 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'pvt tables &amp; KPIs'!$A$55:$A$56</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$A$55:$A$60</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>Central</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'pvt tables &amp; KPIs'!$C$55:$C$56</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$C$55:$C$60</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4002,7 +4246,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-08C0-40E0-80AA-E99945D0A891}"/>
+              <c16:uniqueId val="{00000005-4DD7-46F4-BBF6-05955A785ECB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4129,9 +4373,12 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -4154,23 +4401,9 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:gradFill>
-      <a:gsLst>
-        <a:gs pos="84000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="19000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="40000"/>
-            <a:lumOff val="60000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:lin ang="5400000" scaled="1"/>
-    </a:gradFill>
+    <a:solidFill>
+      <a:sysClr val="window" lastClr="FFFFFF"/>
+    </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
@@ -4229,7 +4462,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Workforce &amp; sales.xlsx]pvt tables &amp; KPIs!PivotTable8</c:name>
+    <c:name>[Ecommerce_Sales_ Project.xlsx]pvt tables &amp; KPIs!PivotTable8</c:name>
     <c:fmtId val="14"/>
   </c:pivotSource>
   <c:chart>
@@ -4242,7 +4475,7 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="bg1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -4252,7 +4485,7 @@
             <a:r>
               <a:rPr lang="en-GB" b="1">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="bg1"/>
                 </a:solidFill>
               </a:rPr>
               <a:t>Delivery</a:t>
@@ -4260,14 +4493,14 @@
             <a:r>
               <a:rPr lang="en-GB" b="1" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="bg1"/>
                 </a:solidFill>
               </a:rPr>
               <a:t> Status</a:t>
             </a:r>
             <a:endParaRPr lang="en-GB" b="1">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -4275,7 +4508,9 @@
       </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:srgbClr val="009999"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -4288,7 +4523,7 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -4482,7 +4717,7 @@
         <c:idx val="5"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent2"/>
+            <a:srgbClr val="7030A0"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -4543,7 +4778,7 @@
         <c:idx val="6"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent2"/>
+            <a:srgbClr val="008080"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -4562,7 +4797,7 @@
         <c:idx val="7"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent2"/>
+            <a:srgbClr val="A18313"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -4581,7 +4816,7 @@
         <c:idx val="8"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent2"/>
+            <a:srgbClr val="7030A0"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -4654,12 +4889,17 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </c:spPr>
           <c:dPt>
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="008080"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -4684,7 +4924,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="A18313"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -4709,7 +4949,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent6"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -4784,13 +5024,16 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'pvt tables &amp; KPIs'!$A$21:$A$23</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$A$21:$A$24</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>Cancelled</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>Delivered</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>In Transit</c:v>
                 </c:pt>
               </c:strCache>
@@ -4798,15 +5041,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'pvt tables &amp; KPIs'!$B$21:$B$23</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$B$21:$B$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4851,7 +5097,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -4876,23 +5122,9 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:gradFill>
-      <a:gsLst>
-        <a:gs pos="84000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="19000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="40000"/>
-            <a:lumOff val="60000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:lin ang="5400000" scaled="1"/>
-    </a:gradFill>
+    <a:solidFill>
+      <a:sysClr val="window" lastClr="FFFFFF"/>
+    </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
@@ -4951,7 +5183,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Workforce &amp; sales.xlsx]pvt tables &amp; KPIs!PivotTable11</c:name>
+    <c:name>[Ecommerce_Sales_ Project.xlsx]pvt tables &amp; KPIs!PivotTable11</c:name>
     <c:fmtId val="29"/>
   </c:pivotSource>
   <c:chart>
@@ -4964,7 +5196,7 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="bg1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -4972,20 +5204,36 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" b="1"/>
+              <a:rPr lang="en-US" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t>Average</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" b="1" baseline="0"/>
+              <a:rPr lang="en-US" b="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t> Delivery Time By Region</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" b="1"/>
+            <a:endParaRPr lang="en-US" b="1">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -4998,7 +5246,7 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -5128,9 +5376,19 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent5"/>
-          </a:solidFill>
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="84000">
+                <a:srgbClr val="021244"/>
+              </a:gs>
+              <a:gs pos="32000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="1"/>
+          </a:gradFill>
           <a:ln>
             <a:noFill/>
           </a:ln>
@@ -5156,7 +5414,7 @@
               <a:pPr>
                 <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:schemeClr val="bg1"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -5238,9 +5496,19 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5"/>
-            </a:solidFill>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="84000">
+                  <a:srgbClr val="021244"/>
+                </a:gs>
+                <a:gs pos="32000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="1"/>
+            </a:gradFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -5263,7 +5531,7 @@
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1"/>
+                      <a:schemeClr val="bg1"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -5302,23 +5570,47 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'pvt tables &amp; KPIs'!$B$36:$B$37</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$B$36:$B$41</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>Central</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'pvt tables &amp; KPIs'!$C$36:$C$37</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$C$36:$C$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5444,23 +5736,9 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:gradFill>
-      <a:gsLst>
-        <a:gs pos="84000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="19000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="40000"/>
-            <a:lumOff val="60000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:lin ang="5400000" scaled="1"/>
-    </a:gradFill>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
@@ -5522,20 +5800,20 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Workforce &amp; sales.xlsx]pvt tables &amp; KPIs!PivotTable10</c:name>
+    <c:name>[Ecommerce_Sales_ Project.xlsx]pvt tables &amp; KPIs!PivotTable10</c:name>
     <c:fmtId val="26"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="0"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="bg1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -5545,7 +5823,7 @@
             <a:r>
               <a:rPr lang="en-US" b="1">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="bg1"/>
                 </a:solidFill>
               </a:rPr>
               <a:t>Sales</a:t>
@@ -5553,14 +5831,14 @@
             <a:r>
               <a:rPr lang="en-US" b="1" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1"/>
+                  <a:schemeClr val="bg1"/>
                 </a:solidFill>
               </a:rPr>
               <a:t> By Month</a:t>
             </a:r>
             <a:endParaRPr lang="en-US" b="1">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:endParaRPr>
           </a:p>
@@ -5568,20 +5846,24 @@
       </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
       <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="0"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -5741,7 +6023,9 @@
         <c:spPr>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -5752,11 +6036,13 @@
           <c:size val="5"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="A18313"/>
             </a:solidFill>
             <a:ln w="9525">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
             </a:ln>
             <a:effectLst/>
@@ -5778,7 +6064,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
@@ -5801,6 +6087,212 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="A18313"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="A18313"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -5825,7 +6317,9 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5836,16 +6330,388 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="A18313"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="A18313"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-E034-4651-ACDD-DF63AB03B7E1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="A18313"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-249B-4934-99D5-32697F6023FB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="A18313"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-249B-4934-99D5-32697F6023FB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="A18313"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-249B-4934-99D5-32697F6023FB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="A18313"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-E034-4651-ACDD-DF63AB03B7E1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="A18313"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000008-FEE5-423C-BFCF-B53939B8F245}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="A18313"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-FEE5-423C-BFCF-B53939B8F245}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="A18313"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-586D-4BA9-934F-804B7EEB9503}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="A18313"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000A-FEE5-423C-BFCF-B53939B8F245}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="10"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="A18313"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="75000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000E-8A8F-45D1-884C-D8EAE3BC0460}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -5861,7 +6727,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
@@ -5903,41 +6769,89 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'pvt tables &amp; KPIs'!$A$120:$A$124</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$A$120:$A$132</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Jun</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>Jul</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
                   <c:v>Aug</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dec</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'pvt tables &amp; KPIs'!$B$120:$B$124</c:f>
+              <c:f>'pvt tables &amp; KPIs'!$B$120:$B$132</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>685</c:v>
+                  <c:v>1099</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>829</c:v>
+                  <c:v>3712</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>315</c:v>
+                  <c:v>905</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>291</c:v>
+                  <c:v>2637</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4940</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2599</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3315</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>782</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1570</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2920</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6312</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4467</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6070,23 +6984,9 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:gradFill>
-      <a:gsLst>
-        <a:gs pos="84000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="19000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="40000"/>
-            <a:lumOff val="60000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:lin ang="5400000" scaled="1"/>
-    </a:gradFill>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
@@ -10109,15 +11009,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>11502</xdr:colOff>
+      <xdr:colOff>378286</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>69012</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>172528</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>126520</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>195061</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>172528</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10132,17 +11032,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1724462" y="0"/>
-          <a:ext cx="17413856" cy="7890294"/>
+          <a:off x="2092067" y="69012"/>
+          <a:ext cx="10996609" cy="7280693"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="60000"/>
-            <a:lumOff val="40000"/>
-          </a:schemeClr>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -10154,9 +11051,9 @@
         </a:ln>
         <a:effectLst>
           <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-            <a:prstClr val="black">
+            <a:srgbClr val="996633">
               <a:alpha val="40000"/>
-            </a:prstClr>
+            </a:srgbClr>
           </a:outerShdw>
         </a:effectLst>
       </xdr:spPr>
@@ -10196,9 +11093,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>24646</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>126520</xdr:rowOff>
+      <xdr:colOff>431322</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>138023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'pvt tables &amp; KPIs'!D86:D88">
       <xdr:nvSpPr>
@@ -10214,15 +11111,13 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1737606" cy="7890294"/>
+          <a:ext cx="2145103" cy="7315200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
+          <a:srgbClr val="2B4463"/>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
@@ -10230,11 +11125,6 @@
           </a:solidFill>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-            <a:prstClr val="black">
-              <a:alpha val="40000"/>
-            </a:prstClr>
-          </a:outerShdw>
           <a:softEdge rad="0"/>
         </a:effectLst>
       </xdr:spPr>
@@ -10274,16 +11164,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>127031</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>574325</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>108178</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>591526</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>299048</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>110911</xdr:rowOff>
+      <xdr:rowOff>149525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'pvt tables &amp; KPIs'!C78">
       <xdr:nvSpPr>
@@ -10298,8 +11188,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="127031" y="1217288"/>
-          <a:ext cx="834198" cy="372437"/>
+          <a:off x="4151412" y="1212359"/>
+          <a:ext cx="966927" cy="409407"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10329,11 +11219,6 @@
           <a:tileRect/>
         </a:gradFill>
         <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="88900" dir="5400000" algn="ctr" rotWithShape="0">
-            <a:schemeClr val="accent6">
-              <a:lumMod val="50000"/>
-            </a:schemeClr>
-          </a:outerShdw>
           <a:softEdge rad="673100"/>
         </a:effectLst>
       </xdr:spPr>
@@ -10384,7 +11269,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr marL="0" indent="0" algn="l"/>
-            <a:t>2,120</a:t>
+            <a:t>35,258</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike">
             <a:gradFill>
@@ -10419,16 +11304,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>114707</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>105911</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>463270</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>95847</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>612065</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>32042</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>335471</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>79872</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'pvt tables &amp; KPIs'!D86:D88">
       <xdr:nvSpPr>
@@ -10443,19 +11328,69 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="114707" y="1954428"/>
-          <a:ext cx="867061" cy="295835"/>
+          <a:off x="5910692" y="1150186"/>
+          <a:ext cx="1118238" cy="335473"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
+        <a:gradFill flip="none" rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="32000">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="53000">
+              <a:schemeClr val="accent5">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="accent5">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="130000" r="50000" b="-30000"/>
+          </a:path>
+          <a:tileRect/>
+        </a:gradFill>
+        <a:ln>
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="65000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="45000"/>
+                  <a:lumOff val="55000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="83000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="45000"/>
+                  <a:lumOff val="55000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="30000"/>
+                  <a:lumOff val="70000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="1"/>
+          </a:gradFill>
+        </a:ln>
         <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="88900" dir="5400000" algn="ctr" rotWithShape="0">
-            <a:schemeClr val="accent6">
-              <a:lumMod val="50000"/>
-            </a:schemeClr>
-          </a:outerShdw>
           <a:softEdge rad="673100"/>
         </a:effectLst>
       </xdr:spPr>
@@ -10482,20 +11417,21 @@
             <a:rPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike">
               <a:gradFill>
                 <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="50000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="63000">
-                    <a:schemeClr val="accent1">
+                  <a:gs pos="16000">
+                    <a:schemeClr val="accent5">
                       <a:lumMod val="60000"/>
                       <a:lumOff val="40000"/>
                     </a:schemeClr>
                   </a:gs>
-                  <a:gs pos="27279">
+                  <a:gs pos="68000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="35000">
                     <a:schemeClr val="accent1">
-                      <a:lumMod val="75000"/>
+                      <a:lumMod val="30000"/>
+                      <a:lumOff val="70000"/>
                     </a:schemeClr>
                   </a:gs>
                 </a:gsLst>
@@ -10511,20 +11447,21 @@
           <a:endParaRPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike">
             <a:gradFill>
               <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="63000">
-                  <a:schemeClr val="accent1">
+                <a:gs pos="16000">
+                  <a:schemeClr val="accent5">
                     <a:lumMod val="60000"/>
                     <a:lumOff val="40000"/>
                   </a:schemeClr>
                 </a:gs>
-                <a:gs pos="27279">
+                <a:gs pos="68000">
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="35000">
                   <a:schemeClr val="accent1">
-                    <a:lumMod val="75000"/>
+                    <a:lumMod val="30000"/>
+                    <a:lumOff val="70000"/>
                   </a:schemeClr>
                 </a:gs>
               </a:gsLst>
@@ -10541,16 +11478,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>100741</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>125315</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>225346</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>61343</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>487442</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>18894</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>23004</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'pvt tables &amp; KPIs'!I99">
       <xdr:nvSpPr>
@@ -10565,19 +11502,19 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="100741" y="2713239"/>
-          <a:ext cx="756404" cy="263284"/>
+          <a:off x="8150146" y="1165524"/>
+          <a:ext cx="1039862" cy="306717"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
         <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="88900" dir="5400000" algn="ctr" rotWithShape="0">
-            <a:schemeClr val="accent6">
-              <a:lumMod val="50000"/>
-            </a:schemeClr>
-          </a:outerShdw>
           <a:softEdge rad="673100"/>
         </a:effectLst>
       </xdr:spPr>
@@ -10602,56 +11539,20 @@
           <a:pPr marL="0" indent="0" algn="l"/>
           <a:fld id="{A7E45D8B-4802-4074-8EF2-58CCECD0D190}" type="TxLink">
             <a:rPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike">
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="50000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="63000">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="60000"/>
-                      <a:lumOff val="40000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="27279">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="75000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
               <a:latin typeface="Aptos display"/>
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr marL="0" indent="0" algn="l"/>
-            <a:t>100.00%</a:t>
+            <a:t>32.35%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike">
-            <a:gradFill>
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="63000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="27279">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="1"/>
-            </a:gradFill>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
             <a:latin typeface="Aptos display"/>
             <a:ea typeface="Calibri"/>
             <a:cs typeface="Calibri"/>
@@ -10663,16 +11564,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>72486</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>170886</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>517224</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>69011</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>790344</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>147880</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>460714</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>29392</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'pvt tables &amp; KPIs'!D107:D108">
       <xdr:nvSpPr>
@@ -10687,19 +11588,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="72486" y="3498217"/>
-          <a:ext cx="1087561" cy="346699"/>
+          <a:off x="10305329" y="1173192"/>
+          <a:ext cx="1185694" cy="328441"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:noFill/>
         <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="88900" dir="5400000" algn="ctr" rotWithShape="0">
-            <a:schemeClr val="accent6">
-              <a:lumMod val="50000"/>
-            </a:schemeClr>
-          </a:outerShdw>
           <a:softEdge rad="673100"/>
         </a:effectLst>
       </xdr:spPr>
@@ -10724,56 +11620,20 @@
           <a:pPr marL="0" indent="0" algn="l"/>
           <a:fld id="{160FDD13-2D56-4418-B8E7-B226355DD71C}" type="TxLink">
             <a:rPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike">
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="50000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="63000">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="60000"/>
-                      <a:lumOff val="40000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="27279">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="75000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="1"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
               <a:latin typeface="Aptos display"/>
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr marL="0" indent="0" algn="l"/>
-            <a:t>Bluetooth Speaker</a:t>
+            <a:t>Leg Set</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike">
-            <a:gradFill>
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="63000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="27279">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="1"/>
-            </a:gradFill>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
             <a:latin typeface="Aptos display"/>
             <a:ea typeface="Calibri"/>
             <a:cs typeface="Calibri"/>
@@ -10785,16 +11645,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>111825</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>171169</xdr:rowOff>
+      <xdr:rowOff>159749</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>973553</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>335474</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>61618</xdr:rowOff>
+      <xdr:rowOff>159748</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10809,27 +11669,19 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="910576"/>
-          <a:ext cx="1343256" cy="260152"/>
+          <a:off x="3690190" y="862642"/>
+          <a:ext cx="1469686" cy="351445"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
+          <a:schemeClr val="bg1"/>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:noFill/>
         </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-            <a:schemeClr val="accent6">
-              <a:lumMod val="50000"/>
-            </a:schemeClr>
-          </a:outerShdw>
-        </a:effectLst>
+        <a:effectLst/>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
@@ -10850,7 +11702,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-GB" sz="1200">
+            <a:rPr lang="en-GB" sz="1400">
               <a:solidFill>
                 <a:schemeClr val="accent6">
                   <a:lumMod val="50000"/>
@@ -10860,29 +11712,27 @@
             <a:t>💰</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="1200" b="1">
+            <a:rPr lang="en-GB" sz="1400" b="1">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="Aptos display"/>
             </a:rPr>
             <a:t>Total</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="1200" b="1" baseline="0">
+            <a:rPr lang="en-GB" sz="1400" b="1" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="Aptos display"/>
             </a:rPr>
             <a:t> </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="1200" b="1" baseline="0">
+            <a:rPr lang="en-GB" sz="1400" b="1" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="Aptos display"/>
               <a:ea typeface="+mn-ea"/>
@@ -10897,16 +11747,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>30967</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>191699</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>158764</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>98590</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>335473</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>111823</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10921,27 +11771,19 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1694633"/>
-          <a:ext cx="1392550" cy="252474"/>
+          <a:off x="5639121" y="861657"/>
+          <a:ext cx="1389811" cy="304505"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:noFill/>
         </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-            <a:schemeClr val="accent6">
-              <a:lumMod val="50000"/>
-            </a:schemeClr>
-          </a:outerShdw>
-        </a:effectLst>
+        <a:effectLst/>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
@@ -10962,37 +11804,37 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-GB" sz="1200"/>
+            <a:rPr lang="en-GB" sz="1400"/>
             <a:t>🔝</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="1200" b="1">
+            <a:rPr lang="en-GB" sz="1400" b="1">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>Total</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="1200" baseline="0">
+            <a:rPr lang="en-GB" sz="1400" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t> </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="1200" b="1" baseline="0">
+            <a:rPr lang="en-GB" sz="1400" b="1" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="Aptos display"/>
             </a:rPr>
             <a:t>region</a:t>
           </a:r>
-          <a:endParaRPr lang="en-GB" sz="1200" b="1">
+          <a:endParaRPr lang="en-GB" sz="1400" b="1">
             <a:solidFill>
-              <a:schemeClr val="bg1"/>
+              <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
             <a:latin typeface="Aptos display"/>
           </a:endParaRPr>
@@ -11003,16 +11845,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>86264</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>44788</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>312468</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>138021</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>30170</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>150317</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>402566</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>115019</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11027,16 +11869,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="86264" y="2447861"/>
-          <a:ext cx="1336456" cy="290380"/>
+          <a:off x="7616167" y="874142"/>
+          <a:ext cx="1953403" cy="345058"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:noFill/>
@@ -11061,6 +11901,17 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
+            <a:rPr lang="en-GB" sz="1600" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos display"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>🚚% Fast Delivery </a:t>
+          </a:r>
+          <a:r>
             <a:rPr lang="en-GB" sz="1200" b="1" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
@@ -11069,7 +11920,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>🚚% Fast delivery</a:t>
+            <a:t>delivery</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -11078,16 +11929,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>68701</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>99380</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>308324</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>163280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>901596</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>24420</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>262604</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>88321</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11102,16 +11953,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="68701" y="3241860"/>
-          <a:ext cx="1202598" cy="294743"/>
+          <a:off x="10116878" y="866173"/>
+          <a:ext cx="1200317" cy="276487"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:noFill/>
@@ -11136,13 +11985,17 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-GB" sz="1200"/>
+            <a:rPr lang="en-GB" sz="1400">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>🥇</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="1200" b="1" baseline="0">
+            <a:rPr lang="en-GB" sz="1400" b="1" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="Aptos display"/>
               <a:ea typeface="+mn-ea"/>
@@ -11151,15 +12004,18 @@
             <a:t>Top</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="1200" b="1" baseline="0">
+            <a:rPr lang="en-GB" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
               <a:latin typeface="Aptos display"/>
             </a:rPr>
             <a:t> </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="1200" b="1" baseline="0">
+            <a:rPr lang="en-GB" sz="1400" b="1" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="bg1"/>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="Aptos display"/>
               <a:ea typeface="+mn-ea"/>
@@ -11175,15 +12031,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>377918</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>135558</xdr:rowOff>
+      <xdr:colOff>466017</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>803</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>135557</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>172527</xdr:rowOff>
+      <xdr:colOff>222868</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>111825</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11213,15 +12069,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>421256</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>135559</xdr:rowOff>
+      <xdr:colOff>385777</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>161214</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>147882</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>172527</xdr:rowOff>
+      <xdr:colOff>112405</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>111824</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11250,16 +12106,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>552092</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>125697</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>395946</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>95848</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>283439</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>36969</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>111825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>47925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11288,16 +12144,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>517586</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>117484</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>106366</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>78018</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>609467</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>128987</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>355894</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>153554</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
       <mc:Choice Requires="a14">
@@ -11333,8 +12189,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="13321650" y="2335705"/>
-              <a:ext cx="1940400" cy="1120613"/>
+              <a:off x="106366" y="3599004"/>
+              <a:ext cx="1957206" cy="1307881"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -11366,16 +12222,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>517584</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>20540</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>102239</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>169234</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>609465</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>12323</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>353869</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>67495</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
       <mc:Choice Requires="a14">
@@ -11411,8 +12267,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="13321648" y="3532723"/>
-              <a:ext cx="1940400" cy="1655449"/>
+              <a:off x="102239" y="5098614"/>
+              <a:ext cx="1959308" cy="1658754"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -11444,16 +12300,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>537303</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>94480</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>113453</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>173286</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>12324</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>24648</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>352098</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>94965</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
       <mc:Choice Requires="a14">
@@ -11489,8 +12345,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="13341367" y="833887"/>
-              <a:ext cx="1939711" cy="1408982"/>
+              <a:off x="113453" y="1757729"/>
+              <a:ext cx="1946323" cy="1682173"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -11523,15 +12379,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>299051</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>147881</xdr:rowOff>
+      <xdr:colOff>567833</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>12257</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>61619</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>12323</xdr:rowOff>
+      <xdr:colOff>329614</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>143772</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11560,16 +12416,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>261258</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>110910</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>344621</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>63900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>12324</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>24647</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>75144</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>31950</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11599,15 +12455,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>295764</xdr:colOff>
+      <xdr:colOff>495223</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>86266</xdr:rowOff>
+      <xdr:rowOff>84573</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>209500</xdr:colOff>
+      <xdr:colOff>101489</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>160205</xdr:rowOff>
+      <xdr:rowOff>159750</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11622,34 +12478,48 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2008724" y="86266"/>
-          <a:ext cx="11004840" cy="813346"/>
+          <a:off x="2203592" y="84573"/>
+          <a:ext cx="10871348" cy="819416"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
         </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="77000">
+              <a:schemeClr val="accent5">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="21000">
+              <a:schemeClr val="accent5">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="51000">
+              <a:schemeClr val="accent5">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="0" scaled="0"/>
+        </a:gradFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-            <a:prstClr val="black">
-              <a:alpha val="40000"/>
-            </a:prstClr>
-          </a:outerShdw>
+          <a:glow rad="127000">
+            <a:schemeClr val="accent6">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:glow>
         </a:effectLst>
         <a:scene3d>
           <a:camera prst="orthographicFront">
             <a:rot lat="0" lon="0" rev="0"/>
           </a:camera>
-          <a:lightRig rig="glow" dir="t">
-            <a:rot lat="0" lon="0" rev="14100000"/>
-          </a:lightRig>
+          <a:lightRig rig="threePt" dir="t"/>
         </a:scene3d>
         <a:sp3d prstMaterial="softEdge">
           <a:bevelT w="127000" prst="artDeco"/>
@@ -11677,96 +12547,34 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-GB" sz="3600"/>
-            <a:t>E-Commerce </a:t>
+            <a:rPr lang="en-GB" sz="4000">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>E-Commerce</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="3600" i="0" u="none" baseline="0"/>
+            <a:rPr lang="en-GB" sz="4000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="4000" i="0" u="none" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>Sales Intelligence Dashboard</a:t>
           </a:r>
-          <a:endParaRPr lang="en-GB" sz="3600" i="0" u="none"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>172528</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>98589</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>739407</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>147881</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E08A9589-F1B4-4D22-A0F5-B2E3422883D0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="172528" y="283440"/>
-          <a:ext cx="936582" cy="418997"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="accent6">
-              <a:lumMod val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>🛒</a:t>
-          </a:r>
+          <a:endParaRPr lang="en-GB" sz="4000" i="0" u="none">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -16576,19 +17384,19 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559625FF-66A8-4B0F-91FC-2F250084A8B1}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A85:B87" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C7D379E-527A-4030-ADBC-E3B088C5A9B4}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A69:A70" firstHeaderRow="1" firstDataRow="1" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0">
       <items count="6">
         <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -16684,17 +17492,17 @@
     <pivotField showAll="0">
       <items count="6">
         <item x="3"/>
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
         <item x="4"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0">
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
       <items count="4">
         <item x="0"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item x="2"/>
         <item t="default"/>
       </items>
@@ -16728,20 +17536,15 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
+  <rowItems count="1">
+    <i/>
   </rowItems>
   <colItems count="1">
     <i/>
   </colItems>
+  <pageFields count="1">
+    <pageField fld="8" hier="-1"/>
+  </pageFields>
   <dataFields count="1">
     <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
@@ -16758,191 +17561,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{21682CE4-5DA1-4DFF-A9E9-693EDC56DE39}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A97:C99" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{98F779D1-3C0B-43D9-8E7B-5AC7A632D257}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="A7:G14" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="19">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="83">
-        <item x="33"/>
-        <item x="50"/>
-        <item x="54"/>
-        <item x="14"/>
-        <item x="49"/>
-        <item x="61"/>
-        <item x="24"/>
-        <item x="0"/>
-        <item x="67"/>
-        <item x="32"/>
-        <item x="31"/>
-        <item x="4"/>
-        <item x="43"/>
-        <item x="16"/>
-        <item x="37"/>
-        <item x="53"/>
-        <item x="15"/>
-        <item x="20"/>
-        <item x="8"/>
-        <item x="12"/>
-        <item x="47"/>
-        <item x="46"/>
-        <item x="42"/>
-        <item x="28"/>
-        <item x="64"/>
-        <item x="62"/>
-        <item x="71"/>
-        <item x="38"/>
-        <item x="70"/>
-        <item x="26"/>
-        <item x="52"/>
-        <item x="36"/>
-        <item x="81"/>
-        <item x="34"/>
-        <item x="22"/>
-        <item x="7"/>
-        <item x="41"/>
-        <item x="65"/>
-        <item x="60"/>
-        <item x="30"/>
-        <item x="72"/>
-        <item x="56"/>
-        <item x="21"/>
-        <item x="5"/>
-        <item x="39"/>
-        <item x="10"/>
-        <item x="25"/>
-        <item x="57"/>
-        <item x="27"/>
-        <item x="45"/>
-        <item x="63"/>
-        <item x="6"/>
-        <item x="29"/>
-        <item x="69"/>
-        <item x="17"/>
-        <item x="48"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="68"/>
-        <item x="1"/>
-        <item x="80"/>
-        <item x="79"/>
-        <item x="23"/>
-        <item x="75"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="78"/>
-        <item x="35"/>
-        <item x="44"/>
-        <item x="40"/>
-        <item x="59"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="55"/>
-        <item x="66"/>
-        <item x="74"/>
-        <item x="51"/>
-        <item x="77"/>
-        <item x="76"/>
-        <item x="19"/>
-        <item x="73"/>
-        <item x="58"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colFields count="1">
-    <field x="17"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A3F58821-18E6-4D05-AACE-82DAD925E85D}" name="PivotTable26" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="69">
-  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="22">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -16953,258 +17574,6 @@
         <item x="0"/>
         <item x="2"/>
         <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5B3A2214-8ABF-47D4-8577-C6D4206D3044}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1">
-      <items count="55">
-        <item x="23"/>
-        <item x="13"/>
-        <item x="36"/>
-        <item x="39"/>
-        <item x="12"/>
-        <item x="43"/>
-        <item x="27"/>
-        <item x="32"/>
-        <item x="7"/>
-        <item x="26"/>
-        <item x="22"/>
-        <item x="18"/>
-        <item x="0"/>
-        <item x="17"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="29"/>
-        <item x="31"/>
-        <item x="19"/>
-        <item x="38"/>
-        <item x="28"/>
-        <item x="21"/>
-        <item x="14"/>
-        <item x="34"/>
-        <item x="11"/>
-        <item x="15"/>
-        <item x="44"/>
-        <item x="1"/>
-        <item x="20"/>
-        <item x="35"/>
-        <item x="6"/>
-        <item x="33"/>
-        <item x="50"/>
-        <item x="42"/>
-        <item x="8"/>
-        <item x="24"/>
-        <item x="30"/>
-        <item x="46"/>
-        <item x="2"/>
-        <item x="40"/>
-        <item x="3"/>
-        <item x="47"/>
-        <item x="25"/>
-        <item x="45"/>
-        <item x="53"/>
-        <item x="49"/>
-        <item x="37"/>
-        <item x="10"/>
-        <item x="52"/>
-        <item x="9"/>
-        <item x="48"/>
-        <item x="51"/>
-        <item x="16"/>
-        <item x="41"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="47"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Customer ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="4" type="count" evalOrder="-1" id="2" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="2" filterVal="2"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0F1A8A33-06F0-48BC-8E01-DB490ACA0BFA}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A77:A78" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="19">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -17300,1241 +17669,17 @@
     <pivotField showAll="0">
       <items count="6">
         <item x="3"/>
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
         <item x="4"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0">
       <items count="4">
         <item x="0"/>
-        <item h="1" x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
         <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB4895FD-898D-4007-9423-4FDF07F61156}" name="PivotTable10" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
-  <location ref="A119:B124" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="83">
-        <item x="33"/>
-        <item x="50"/>
-        <item x="54"/>
-        <item x="14"/>
-        <item x="49"/>
-        <item x="61"/>
-        <item x="24"/>
-        <item x="0"/>
-        <item x="67"/>
-        <item x="32"/>
-        <item x="31"/>
-        <item x="4"/>
-        <item x="43"/>
-        <item x="16"/>
-        <item x="37"/>
-        <item x="53"/>
-        <item x="15"/>
-        <item x="20"/>
-        <item x="8"/>
-        <item x="12"/>
-        <item x="47"/>
-        <item x="46"/>
-        <item x="42"/>
-        <item x="28"/>
-        <item x="64"/>
-        <item x="62"/>
-        <item x="71"/>
-        <item x="38"/>
-        <item x="70"/>
-        <item x="26"/>
-        <item x="52"/>
-        <item x="36"/>
-        <item x="81"/>
-        <item x="34"/>
-        <item x="22"/>
-        <item x="7"/>
-        <item x="41"/>
-        <item x="65"/>
-        <item x="60"/>
-        <item x="30"/>
-        <item x="72"/>
-        <item x="56"/>
-        <item x="21"/>
-        <item x="5"/>
-        <item x="39"/>
-        <item x="10"/>
-        <item x="25"/>
-        <item x="57"/>
-        <item x="27"/>
-        <item x="45"/>
-        <item x="63"/>
-        <item x="6"/>
-        <item x="29"/>
-        <item x="69"/>
-        <item x="17"/>
-        <item x="48"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="68"/>
-        <item x="1"/>
-        <item x="80"/>
-        <item x="79"/>
-        <item x="23"/>
-        <item x="75"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="78"/>
-        <item x="35"/>
-        <item x="44"/>
-        <item x="40"/>
-        <item x="59"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="55"/>
-        <item x="66"/>
-        <item x="74"/>
-        <item x="51"/>
-        <item x="77"/>
-        <item x="76"/>
-        <item x="19"/>
-        <item x="73"/>
-        <item x="58"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="23">
-        <item x="15"/>
-        <item x="16"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="19"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="18"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="12"/>
-        <item x="20"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="8"/>
-        <item x="13"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="26" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A4DA052E-EDD1-4A00-AFA7-F8DD32329725}" name="PivotTable8" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
-  <location ref="A20:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="83">
-        <item x="33"/>
-        <item x="50"/>
-        <item x="54"/>
-        <item x="14"/>
-        <item x="49"/>
-        <item x="61"/>
-        <item x="24"/>
-        <item x="0"/>
-        <item x="67"/>
-        <item x="32"/>
-        <item x="31"/>
-        <item x="4"/>
-        <item x="43"/>
-        <item x="16"/>
-        <item x="37"/>
-        <item x="53"/>
-        <item x="15"/>
-        <item x="20"/>
-        <item x="8"/>
-        <item x="12"/>
-        <item x="47"/>
-        <item x="46"/>
-        <item x="42"/>
-        <item x="28"/>
-        <item x="64"/>
-        <item x="62"/>
-        <item x="71"/>
-        <item x="38"/>
-        <item x="70"/>
-        <item x="26"/>
-        <item x="52"/>
-        <item x="36"/>
-        <item x="81"/>
-        <item x="34"/>
-        <item x="22"/>
-        <item x="7"/>
-        <item x="41"/>
-        <item x="65"/>
-        <item x="60"/>
-        <item x="30"/>
-        <item x="72"/>
-        <item x="56"/>
-        <item x="21"/>
-        <item x="5"/>
-        <item x="39"/>
-        <item x="10"/>
-        <item x="25"/>
-        <item x="57"/>
-        <item x="27"/>
-        <item x="45"/>
-        <item x="63"/>
-        <item x="6"/>
-        <item x="29"/>
-        <item x="69"/>
-        <item x="17"/>
-        <item x="48"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="68"/>
-        <item x="1"/>
-        <item x="80"/>
-        <item x="79"/>
-        <item x="23"/>
-        <item x="75"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="78"/>
-        <item x="35"/>
-        <item x="44"/>
-        <item x="40"/>
-        <item x="59"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="55"/>
-        <item x="66"/>
-        <item x="74"/>
-        <item x="51"/>
-        <item x="77"/>
-        <item x="76"/>
-        <item x="19"/>
-        <item x="73"/>
-        <item x="58"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="23">
-        <item x="15"/>
-        <item x="16"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="19"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="18"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="12"/>
-        <item x="20"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="8"/>
-        <item x="13"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Quantity" fld="5" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="11" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="14" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="14" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="14" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="14" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A4F0F522-3C24-46A9-A6EA-A9F72B59C5F9}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="A53:D56" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="83">
-        <item x="33"/>
-        <item x="50"/>
-        <item x="54"/>
-        <item x="14"/>
-        <item x="49"/>
-        <item x="61"/>
-        <item x="24"/>
-        <item x="0"/>
-        <item x="67"/>
-        <item x="32"/>
-        <item x="31"/>
-        <item x="4"/>
-        <item x="43"/>
-        <item x="16"/>
-        <item x="37"/>
-        <item x="53"/>
-        <item x="15"/>
-        <item x="20"/>
-        <item x="8"/>
-        <item x="12"/>
-        <item x="47"/>
-        <item x="46"/>
-        <item x="42"/>
-        <item x="28"/>
-        <item x="64"/>
-        <item x="62"/>
-        <item x="71"/>
-        <item x="38"/>
-        <item x="70"/>
-        <item x="26"/>
-        <item x="52"/>
-        <item x="36"/>
-        <item x="81"/>
-        <item x="34"/>
-        <item x="22"/>
-        <item x="7"/>
-        <item x="41"/>
-        <item x="65"/>
-        <item x="60"/>
-        <item x="30"/>
-        <item x="72"/>
-        <item x="56"/>
-        <item x="21"/>
-        <item x="5"/>
-        <item x="39"/>
-        <item x="10"/>
-        <item x="25"/>
-        <item x="57"/>
-        <item x="27"/>
-        <item x="45"/>
-        <item x="63"/>
-        <item x="6"/>
-        <item x="29"/>
-        <item x="69"/>
-        <item x="17"/>
-        <item x="48"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="68"/>
-        <item x="1"/>
-        <item x="80"/>
-        <item x="79"/>
-        <item x="23"/>
-        <item x="75"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="78"/>
-        <item x="35"/>
-        <item x="44"/>
-        <item x="40"/>
-        <item x="59"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="55"/>
-        <item x="66"/>
-        <item x="74"/>
-        <item x="51"/>
-        <item x="77"/>
-        <item x="76"/>
-        <item x="19"/>
-        <item x="73"/>
-        <item x="58"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="23">
-        <item x="15"/>
-        <item x="16"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="19"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="18"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="12"/>
-        <item x="20"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="8"/>
-        <item x="13"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="13"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="6" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CA04B0A9-5BD8-4D9C-8AE2-A099459E2ED1}" name="PivotTable11" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="32">
-  <location ref="B35:C37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="83">
-        <item x="33"/>
-        <item x="50"/>
-        <item x="54"/>
-        <item x="14"/>
-        <item x="49"/>
-        <item x="61"/>
-        <item x="24"/>
-        <item x="0"/>
-        <item x="67"/>
-        <item x="32"/>
-        <item x="31"/>
-        <item x="4"/>
-        <item x="43"/>
-        <item x="16"/>
-        <item x="37"/>
-        <item x="53"/>
-        <item x="15"/>
-        <item x="20"/>
-        <item x="8"/>
-        <item x="12"/>
-        <item x="47"/>
-        <item x="46"/>
-        <item x="42"/>
-        <item x="28"/>
-        <item x="64"/>
-        <item x="62"/>
-        <item x="71"/>
-        <item x="38"/>
-        <item x="70"/>
-        <item x="26"/>
-        <item x="52"/>
-        <item x="36"/>
-        <item x="81"/>
-        <item x="34"/>
-        <item x="22"/>
-        <item x="7"/>
-        <item x="41"/>
-        <item x="65"/>
-        <item x="60"/>
-        <item x="30"/>
-        <item x="72"/>
-        <item x="56"/>
-        <item x="21"/>
-        <item x="5"/>
-        <item x="39"/>
-        <item x="10"/>
-        <item x="25"/>
-        <item x="57"/>
-        <item x="27"/>
-        <item x="45"/>
-        <item x="63"/>
-        <item x="6"/>
-        <item x="29"/>
-        <item x="69"/>
-        <item x="17"/>
-        <item x="48"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="68"/>
-        <item x="1"/>
-        <item x="80"/>
-        <item x="79"/>
-        <item x="23"/>
-        <item x="75"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="78"/>
-        <item x="35"/>
-        <item x="44"/>
-        <item x="40"/>
-        <item x="59"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="55"/>
-        <item x="66"/>
-        <item x="74"/>
-        <item x="51"/>
-        <item x="77"/>
-        <item x="76"/>
-        <item x="19"/>
-        <item x="73"/>
-        <item x="58"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="23">
-        <item x="15"/>
-        <item x="16"/>
-        <item x="4"/>
-        <item x="7"/>
-        <item x="19"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="18"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="12"/>
-        <item x="20"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="8"/>
-        <item x="13"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="14" hier="-1"/>
-    <pageField fld="7" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of Average Time" fld="15" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="4">
-    <chartFormat chart="26" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="28" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="29" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{98F779D1-3C0B-43D9-8E7B-5AC7A632D257}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="A7:F10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="83">
-        <item x="33"/>
-        <item x="50"/>
-        <item x="54"/>
-        <item x="14"/>
-        <item x="49"/>
-        <item x="61"/>
-        <item x="24"/>
-        <item x="0"/>
-        <item x="67"/>
-        <item x="32"/>
-        <item x="31"/>
-        <item x="4"/>
-        <item x="43"/>
-        <item x="16"/>
-        <item x="37"/>
-        <item x="53"/>
-        <item x="15"/>
-        <item x="20"/>
-        <item x="8"/>
-        <item x="12"/>
-        <item x="47"/>
-        <item x="46"/>
-        <item x="42"/>
-        <item x="28"/>
-        <item x="64"/>
-        <item x="62"/>
-        <item x="71"/>
-        <item x="38"/>
-        <item x="70"/>
-        <item x="26"/>
-        <item x="52"/>
-        <item x="36"/>
-        <item x="81"/>
-        <item x="34"/>
-        <item x="22"/>
-        <item x="7"/>
-        <item x="41"/>
-        <item x="65"/>
-        <item x="60"/>
-        <item x="30"/>
-        <item x="72"/>
-        <item x="56"/>
-        <item x="21"/>
-        <item x="5"/>
-        <item x="39"/>
-        <item x="10"/>
-        <item x="25"/>
-        <item x="57"/>
-        <item x="27"/>
-        <item x="45"/>
-        <item x="63"/>
-        <item x="6"/>
-        <item x="29"/>
-        <item x="69"/>
-        <item x="17"/>
-        <item x="48"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="68"/>
-        <item x="1"/>
-        <item x="80"/>
-        <item x="79"/>
-        <item x="23"/>
-        <item x="75"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="78"/>
-        <item x="35"/>
-        <item x="44"/>
-        <item x="40"/>
-        <item x="59"/>
-        <item x="11"/>
-        <item x="2"/>
-        <item x="55"/>
-        <item x="66"/>
-        <item x="74"/>
-        <item x="51"/>
-        <item x="77"/>
-        <item x="76"/>
-        <item x="19"/>
-        <item x="73"/>
-        <item x="58"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item h="1" x="1"/>
         <item x="2"/>
         <item t="default"/>
       </items>
@@ -18606,9 +17751,21 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="6">
     <i>
       <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -18617,7 +17774,10 @@
   <colFields count="1">
     <field x="14"/>
   </colFields>
-  <colItems count="5">
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
     <i>
       <x v="1"/>
     </i>
@@ -18780,9 +17940,255 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C29789AC-343E-4047-9031-A3D1EC5942E3}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A106:B112" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A3F58821-18E6-4D05-AACE-82DAD925E85D}" name="PivotTable26" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="69">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="22">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5B3A2214-8ABF-47D4-8577-C6D4206D3044}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+      <items count="55">
+        <item x="23"/>
+        <item x="13"/>
+        <item x="36"/>
+        <item x="39"/>
+        <item x="12"/>
+        <item x="43"/>
+        <item x="27"/>
+        <item x="32"/>
+        <item x="7"/>
+        <item x="26"/>
+        <item x="22"/>
+        <item x="18"/>
+        <item x="0"/>
+        <item x="17"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="29"/>
+        <item x="31"/>
+        <item x="19"/>
+        <item x="38"/>
+        <item x="28"/>
+        <item x="21"/>
+        <item x="14"/>
+        <item x="34"/>
+        <item x="11"/>
+        <item x="15"/>
+        <item x="44"/>
+        <item x="1"/>
+        <item x="20"/>
+        <item x="35"/>
+        <item x="6"/>
+        <item x="33"/>
+        <item x="50"/>
+        <item x="42"/>
+        <item x="8"/>
+        <item x="24"/>
+        <item x="30"/>
+        <item x="46"/>
+        <item x="2"/>
+        <item x="40"/>
+        <item x="3"/>
+        <item x="47"/>
+        <item x="25"/>
+        <item x="45"/>
+        <item x="53"/>
+        <item x="49"/>
+        <item x="37"/>
+        <item x="10"/>
+        <item x="52"/>
+        <item x="9"/>
+        <item x="48"/>
+        <item x="51"/>
+        <item x="16"/>
+        <item x="41"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Customer ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="4" type="count" evalOrder="-1" id="2" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="2" filterVal="2"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB4895FD-898D-4007-9423-4FDF07F61156}" name="PivotTable10" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="27">
+  <location ref="A119:B132" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -18790,10 +18196,1511 @@
     <pivotField showAll="0">
       <items count="6">
         <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="83">
+        <item x="33"/>
+        <item x="50"/>
+        <item x="54"/>
+        <item x="14"/>
+        <item x="49"/>
+        <item x="61"/>
+        <item x="24"/>
+        <item x="0"/>
+        <item x="67"/>
+        <item x="32"/>
+        <item x="31"/>
+        <item x="4"/>
+        <item x="43"/>
+        <item x="16"/>
+        <item x="37"/>
+        <item x="53"/>
+        <item x="15"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="12"/>
+        <item x="47"/>
+        <item x="46"/>
+        <item x="42"/>
+        <item x="28"/>
+        <item x="64"/>
+        <item x="62"/>
+        <item x="71"/>
+        <item x="38"/>
+        <item x="70"/>
+        <item x="26"/>
+        <item x="52"/>
+        <item x="36"/>
+        <item x="81"/>
+        <item x="34"/>
+        <item x="22"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="65"/>
+        <item x="60"/>
+        <item x="30"/>
+        <item x="72"/>
+        <item x="56"/>
+        <item x="21"/>
+        <item x="5"/>
+        <item x="39"/>
+        <item x="10"/>
+        <item x="25"/>
+        <item x="57"/>
+        <item x="27"/>
+        <item x="45"/>
+        <item x="63"/>
+        <item x="6"/>
+        <item x="29"/>
+        <item x="69"/>
+        <item x="17"/>
+        <item x="48"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="68"/>
+        <item x="1"/>
+        <item x="80"/>
+        <item x="79"/>
+        <item x="23"/>
+        <item x="75"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="78"/>
+        <item x="35"/>
+        <item x="44"/>
+        <item x="40"/>
+        <item x="59"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="55"/>
+        <item x="66"/>
+        <item x="74"/>
+        <item x="51"/>
+        <item x="77"/>
+        <item x="76"/>
+        <item x="19"/>
+        <item x="73"/>
+        <item x="58"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="23">
+        <item x="15"/>
+        <item x="16"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="19"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="18"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="12"/>
+        <item x="20"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="8"/>
+        <item x="13"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="11">
+    <chartFormat chart="26" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="10" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="10" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="10" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="10" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="10" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="10" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="10" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="10" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="10" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="26" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="10" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{559625FF-66A8-4B0F-91FC-2F250084A8B1}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A85:B91" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="83">
+        <item x="33"/>
+        <item x="50"/>
+        <item x="54"/>
+        <item x="14"/>
+        <item x="49"/>
+        <item x="61"/>
+        <item x="24"/>
+        <item x="0"/>
+        <item x="67"/>
+        <item x="32"/>
+        <item x="31"/>
+        <item x="4"/>
+        <item x="43"/>
+        <item x="16"/>
+        <item x="37"/>
+        <item x="53"/>
+        <item x="15"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="12"/>
+        <item x="47"/>
+        <item x="46"/>
+        <item x="42"/>
+        <item x="28"/>
+        <item x="64"/>
+        <item x="62"/>
+        <item x="71"/>
+        <item x="38"/>
+        <item x="70"/>
+        <item x="26"/>
+        <item x="52"/>
+        <item x="36"/>
+        <item x="81"/>
+        <item x="34"/>
+        <item x="22"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="65"/>
+        <item x="60"/>
+        <item x="30"/>
+        <item x="72"/>
+        <item x="56"/>
+        <item x="21"/>
+        <item x="5"/>
+        <item x="39"/>
+        <item x="10"/>
+        <item x="25"/>
+        <item x="57"/>
+        <item x="27"/>
+        <item x="45"/>
+        <item x="63"/>
+        <item x="6"/>
+        <item x="29"/>
+        <item x="69"/>
+        <item x="17"/>
+        <item x="48"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="68"/>
+        <item x="1"/>
+        <item x="80"/>
+        <item x="79"/>
+        <item x="23"/>
+        <item x="75"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="78"/>
+        <item x="35"/>
+        <item x="44"/>
+        <item x="40"/>
+        <item x="59"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="55"/>
+        <item x="66"/>
+        <item x="74"/>
+        <item x="51"/>
+        <item x="77"/>
+        <item x="76"/>
+        <item x="19"/>
+        <item x="73"/>
+        <item x="58"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CA04B0A9-5BD8-4D9C-8AE2-A099459E2ED1}" name="PivotTable11" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="32">
+  <location ref="B35:C41" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="83">
+        <item x="33"/>
+        <item x="50"/>
+        <item x="54"/>
+        <item x="14"/>
+        <item x="49"/>
+        <item x="61"/>
+        <item x="24"/>
+        <item x="0"/>
+        <item x="67"/>
+        <item x="32"/>
+        <item x="31"/>
+        <item x="4"/>
+        <item x="43"/>
+        <item x="16"/>
+        <item x="37"/>
+        <item x="53"/>
+        <item x="15"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="12"/>
+        <item x="47"/>
+        <item x="46"/>
+        <item x="42"/>
+        <item x="28"/>
+        <item x="64"/>
+        <item x="62"/>
+        <item x="71"/>
+        <item x="38"/>
+        <item x="70"/>
+        <item x="26"/>
+        <item x="52"/>
+        <item x="36"/>
+        <item x="81"/>
+        <item x="34"/>
+        <item x="22"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="65"/>
+        <item x="60"/>
+        <item x="30"/>
+        <item x="72"/>
+        <item x="56"/>
+        <item x="21"/>
+        <item x="5"/>
+        <item x="39"/>
+        <item x="10"/>
+        <item x="25"/>
+        <item x="57"/>
+        <item x="27"/>
+        <item x="45"/>
+        <item x="63"/>
+        <item x="6"/>
+        <item x="29"/>
+        <item x="69"/>
+        <item x="17"/>
+        <item x="48"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="68"/>
+        <item x="1"/>
+        <item x="80"/>
+        <item x="79"/>
+        <item x="23"/>
+        <item x="75"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="78"/>
+        <item x="35"/>
+        <item x="44"/>
+        <item x="40"/>
+        <item x="59"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="55"/>
+        <item x="66"/>
+        <item x="74"/>
+        <item x="51"/>
+        <item x="77"/>
+        <item x="76"/>
+        <item x="19"/>
+        <item x="73"/>
+        <item x="58"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="23">
+        <item x="15"/>
+        <item x="16"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="19"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="18"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="12"/>
+        <item x="20"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="8"/>
+        <item x="13"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="14" hier="-1"/>
+    <pageField fld="7" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Average Time" fld="15" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="26" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="29" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0F1A8A33-06F0-48BC-8E01-DB490ACA0BFA}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A77:A78" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="19">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="83">
+        <item x="33"/>
+        <item x="50"/>
+        <item x="54"/>
+        <item x="14"/>
+        <item x="49"/>
+        <item x="61"/>
+        <item x="24"/>
+        <item x="0"/>
+        <item x="67"/>
+        <item x="32"/>
+        <item x="31"/>
+        <item x="4"/>
+        <item x="43"/>
+        <item x="16"/>
+        <item x="37"/>
+        <item x="53"/>
+        <item x="15"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="12"/>
+        <item x="47"/>
+        <item x="46"/>
+        <item x="42"/>
+        <item x="28"/>
+        <item x="64"/>
+        <item x="62"/>
+        <item x="71"/>
+        <item x="38"/>
+        <item x="70"/>
+        <item x="26"/>
+        <item x="52"/>
+        <item x="36"/>
+        <item x="81"/>
+        <item x="34"/>
+        <item x="22"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="65"/>
+        <item x="60"/>
+        <item x="30"/>
+        <item x="72"/>
+        <item x="56"/>
+        <item x="21"/>
+        <item x="5"/>
+        <item x="39"/>
+        <item x="10"/>
+        <item x="25"/>
+        <item x="57"/>
+        <item x="27"/>
+        <item x="45"/>
+        <item x="63"/>
+        <item x="6"/>
+        <item x="29"/>
+        <item x="69"/>
+        <item x="17"/>
+        <item x="48"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="68"/>
+        <item x="1"/>
+        <item x="80"/>
+        <item x="79"/>
+        <item x="23"/>
+        <item x="75"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="78"/>
+        <item x="35"/>
+        <item x="44"/>
+        <item x="40"/>
+        <item x="59"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="55"/>
+        <item x="66"/>
+        <item x="74"/>
+        <item x="51"/>
+        <item x="77"/>
+        <item x="76"/>
+        <item x="19"/>
+        <item x="73"/>
+        <item x="58"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{21682CE4-5DA1-4DFF-A9E9-693EDC56DE39}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A97:E99" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="83">
+        <item x="33"/>
+        <item x="50"/>
+        <item x="54"/>
+        <item x="14"/>
+        <item x="49"/>
+        <item x="61"/>
+        <item x="24"/>
+        <item x="0"/>
+        <item x="67"/>
+        <item x="32"/>
+        <item x="31"/>
+        <item x="4"/>
+        <item x="43"/>
+        <item x="16"/>
+        <item x="37"/>
+        <item x="53"/>
+        <item x="15"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="12"/>
+        <item x="47"/>
+        <item x="46"/>
+        <item x="42"/>
+        <item x="28"/>
+        <item x="64"/>
+        <item x="62"/>
+        <item x="71"/>
+        <item x="38"/>
+        <item x="70"/>
+        <item x="26"/>
+        <item x="52"/>
+        <item x="36"/>
+        <item x="81"/>
+        <item x="34"/>
+        <item x="22"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="65"/>
+        <item x="60"/>
+        <item x="30"/>
+        <item x="72"/>
+        <item x="56"/>
+        <item x="21"/>
+        <item x="5"/>
+        <item x="39"/>
+        <item x="10"/>
+        <item x="25"/>
+        <item x="57"/>
+        <item x="27"/>
+        <item x="45"/>
+        <item x="63"/>
+        <item x="6"/>
+        <item x="29"/>
+        <item x="69"/>
+        <item x="17"/>
+        <item x="48"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="68"/>
+        <item x="1"/>
+        <item x="80"/>
+        <item x="79"/>
+        <item x="23"/>
+        <item x="75"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="78"/>
+        <item x="35"/>
+        <item x="44"/>
+        <item x="40"/>
+        <item x="59"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="55"/>
+        <item x="66"/>
+        <item x="74"/>
+        <item x="51"/>
+        <item x="77"/>
+        <item x="76"/>
+        <item x="19"/>
+        <item x="73"/>
+        <item x="58"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colFields count="1">
+    <field x="17"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A4F0F522-3C24-46A9-A6EA-A9F72B59C5F9}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="A53:D60" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="83">
+        <item x="33"/>
+        <item x="50"/>
+        <item x="54"/>
+        <item x="14"/>
+        <item x="49"/>
+        <item x="61"/>
+        <item x="24"/>
+        <item x="0"/>
+        <item x="67"/>
+        <item x="32"/>
+        <item x="31"/>
+        <item x="4"/>
+        <item x="43"/>
+        <item x="16"/>
+        <item x="37"/>
+        <item x="53"/>
+        <item x="15"/>
+        <item x="20"/>
+        <item x="8"/>
+        <item x="12"/>
+        <item x="47"/>
+        <item x="46"/>
+        <item x="42"/>
+        <item x="28"/>
+        <item x="64"/>
+        <item x="62"/>
+        <item x="71"/>
+        <item x="38"/>
+        <item x="70"/>
+        <item x="26"/>
+        <item x="52"/>
+        <item x="36"/>
+        <item x="81"/>
+        <item x="34"/>
+        <item x="22"/>
+        <item x="7"/>
+        <item x="41"/>
+        <item x="65"/>
+        <item x="60"/>
+        <item x="30"/>
+        <item x="72"/>
+        <item x="56"/>
+        <item x="21"/>
+        <item x="5"/>
+        <item x="39"/>
+        <item x="10"/>
+        <item x="25"/>
+        <item x="57"/>
+        <item x="27"/>
+        <item x="45"/>
+        <item x="63"/>
+        <item x="6"/>
+        <item x="29"/>
+        <item x="69"/>
+        <item x="17"/>
+        <item x="48"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="68"/>
+        <item x="1"/>
+        <item x="80"/>
+        <item x="79"/>
+        <item x="23"/>
+        <item x="75"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="78"/>
+        <item x="35"/>
+        <item x="44"/>
+        <item x="40"/>
+        <item x="59"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="55"/>
+        <item x="66"/>
+        <item x="74"/>
+        <item x="51"/>
+        <item x="77"/>
+        <item x="76"/>
+        <item x="19"/>
+        <item x="73"/>
+        <item x="58"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="23">
+        <item x="15"/>
+        <item x="16"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="19"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="18"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="12"/>
+        <item x="20"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="8"/>
+        <item x="13"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="13"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Order ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="6" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C29789AC-343E-4047-9031-A3D1EC5942E3}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A106:B109" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18889,17 +19796,17 @@
     <pivotField showAll="0">
       <items count="6">
         <item x="3"/>
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
         <item x="4"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0">
       <items count="4">
         <item x="0"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item x="2"/>
         <item t="default"/>
       </items>
@@ -18962,21 +19869,12 @@
   <rowFields count="1">
     <field x="18"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="3">
     <i>
-      <x v="2"/>
+      <x v="11"/>
     </i>
     <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="17"/>
+      <x v="19"/>
     </i>
     <i t="grand">
       <x/>
@@ -19010,8 +19908,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C7D379E-527A-4030-ADBC-E3B088C5A9B4}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A69:A70" firstHeaderRow="1" firstDataRow="1" firstDataCol="0" rowPageCount="1" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A4DA052E-EDD1-4A00-AFA7-F8DD32329725}" name="PivotTable8" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+  <location ref="A20:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -19019,16 +19917,16 @@
     <pivotField showAll="0">
       <items count="6">
         <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item h="1" x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
       <items count="83">
         <item x="33"/>
         <item x="50"/>
@@ -19118,17 +20016,17 @@
     <pivotField showAll="0">
       <items count="6">
         <item x="3"/>
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
         <item x="4"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="4">
         <item x="0"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item x="2"/>
         <item t="default"/>
       </items>
@@ -19155,25 +20053,124 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="23">
+        <item x="15"/>
+        <item x="16"/>
+        <item x="4"/>
+        <item x="7"/>
+        <item x="19"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="18"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="12"/>
+        <item x="20"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="8"/>
+        <item x="13"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
-  <rowItems count="1">
-    <i/>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
   </rowItems>
   <colItems count="1">
     <i/>
   </colItems>
-  <pageFields count="1">
-    <pageField fld="8" hier="-1"/>
-  </pageFields>
   <dataFields count="1">
-    <dataField name="Sum of Total Amount" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Count of Quantity" fld="5" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="11" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -19204,8 +20201,8 @@
     <tabular pivotCacheId="262064054">
       <items count="3">
         <i x="0" s="1"/>
+        <i x="1" s="1"/>
         <i x="2" s="1"/>
-        <i x="1" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -19231,10 +20228,10 @@
     <tabular pivotCacheId="262064054">
       <items count="5">
         <i x="3" s="1"/>
-        <i x="1"/>
-        <i x="0"/>
-        <i x="2"/>
-        <i x="4"/>
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+        <i x="2" s="1"/>
+        <i x="4" s="1"/>
       </items>
     </tabular>
   </data>
@@ -19260,10 +20257,10 @@
     <tabular pivotCacheId="262064054">
       <items count="5">
         <i x="3" s="1"/>
-        <i x="0"/>
+        <i x="0" s="1"/>
         <i x="1" s="1"/>
         <i x="4" s="1"/>
-        <i x="2"/>
+        <i x="2" s="1"/>
       </items>
     </tabular>
   </data>
@@ -19274,7 +20271,7 @@
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
   <slicer name="Delivery Status 1" xr10:uid="{57379A61-2166-4003-8B4E-E713B7821EB5}" cache="Slicer_Delivery_Status1" caption="Delivery Status" style="SlicerStyleDark5" rowHeight="234710"/>
   <slicer name="Region 2" xr10:uid="{4D3BFCC2-8971-4A1D-941D-4FF96E7DD2A8}" cache="Slicer_Region1" caption="Region" style="SlicerStyleDark5" rowHeight="234710"/>
-  <slicer name="Payment Method 3" xr10:uid="{92E6F10E-BA7C-45FE-8A72-9FF28E29AEE3}" cache="Slicer_Payment_Method1" caption="Payment Method" startItem="1" style="SlicerStyleDark5" rowHeight="234710"/>
+  <slicer name="Payment Method 3" xr10:uid="{92E6F10E-BA7C-45FE-8A72-9FF28E29AEE3}" cache="Slicer_Payment_Method1" caption="Payment Method" style="SlicerStyleDark5" rowHeight="234710"/>
 </slicers>
 </file>
 
@@ -19616,20 +20613,21 @@
     <col min="2" max="2" width="19.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.75" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="A2" s="29" t="s">
         <v>335</v>
       </c>
       <c r="B2" s="28"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
         <v>346</v>
       </c>
@@ -19637,16 +20635,16 @@
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="26"/>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
       <c r="D5" s="20"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="10"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>317</v>
       </c>
@@ -19654,64 +20652,165 @@
         <v>318</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>315</v>
       </c>
       <c r="B8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" t="s">
         <v>200</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>211</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>206</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>203</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>30</v>
       </c>
       <c r="B9" s="14">
-        <v>1056</v>
+        <v>84</v>
       </c>
       <c r="C9" s="14">
-        <v>88</v>
+        <v>2662</v>
       </c>
       <c r="D9" s="14">
-        <v>685</v>
+        <v>210</v>
       </c>
       <c r="E9" s="14">
-        <v>291</v>
+        <v>2063</v>
       </c>
       <c r="F9" s="14">
-        <v>2120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+      <c r="G9" s="14">
+        <v>5456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="14">
+        <v>394</v>
+      </c>
+      <c r="C10" s="14">
+        <v>365</v>
+      </c>
+      <c r="D10" s="14">
+        <v>711</v>
+      </c>
+      <c r="E10" s="14">
+        <v>741</v>
+      </c>
+      <c r="F10" s="14">
+        <v>1424</v>
+      </c>
+      <c r="G10" s="14">
+        <v>3635</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="14">
+        <v>464</v>
+      </c>
+      <c r="C11" s="14">
+        <v>6522</v>
+      </c>
+      <c r="D11" s="14">
+        <v>788</v>
+      </c>
+      <c r="E11" s="14">
+        <v>2131</v>
+      </c>
+      <c r="F11" s="14">
+        <v>586</v>
+      </c>
+      <c r="G11" s="14">
+        <v>10491</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="14">
+        <v>423</v>
+      </c>
+      <c r="C12" s="14">
+        <v>3938</v>
+      </c>
+      <c r="D12" s="14">
+        <v>1032</v>
+      </c>
+      <c r="E12" s="14">
+        <v>1881</v>
+      </c>
+      <c r="F12" s="14">
+        <v>43</v>
+      </c>
+      <c r="G12" s="14">
+        <v>7317</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="14">
+        <v>350</v>
+      </c>
+      <c r="C13" s="14">
+        <v>1722</v>
+      </c>
+      <c r="D13" s="14">
+        <v>1131</v>
+      </c>
+      <c r="E13" s="14">
+        <v>4135</v>
+      </c>
+      <c r="F13" s="14">
+        <v>1021</v>
+      </c>
+      <c r="G13" s="14">
+        <v>8359</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="B10" s="14">
-        <v>1056</v>
-      </c>
-      <c r="C10" s="14">
-        <v>88</v>
-      </c>
-      <c r="D10" s="14">
-        <v>685</v>
-      </c>
-      <c r="E10" s="14">
-        <v>291</v>
-      </c>
-      <c r="F10" s="14">
-        <v>2120</v>
+      <c r="B14" s="14">
+        <v>1715</v>
+      </c>
+      <c r="C14" s="14">
+        <v>15209</v>
+      </c>
+      <c r="D14" s="14">
+        <v>3872</v>
+      </c>
+      <c r="E14" s="14">
+        <v>10951</v>
+      </c>
+      <c r="F14" s="14">
+        <v>3511</v>
+      </c>
+      <c r="G14" s="14">
+        <v>35258</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -19735,23 +20834,31 @@
         <v>14</v>
       </c>
       <c r="B21" s="14">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B22" s="14">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="14">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="B23" s="14">
-        <v>5</v>
+      <c r="B24" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -19801,7 +20908,7 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -19820,15 +20927,47 @@
         <v>30</v>
       </c>
       <c r="C36" s="14">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B37" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="14">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="14">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="C37" s="14">
-        <v>5</v>
+      <c r="C41" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -19902,27 +21041,83 @@
         <v>30</v>
       </c>
       <c r="B55" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C55" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D55" s="14">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B56" s="14">
+        <v>15</v>
+      </c>
+      <c r="C56" s="14">
+        <v>3</v>
+      </c>
+      <c r="D56" s="14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" s="14">
+        <v>15</v>
+      </c>
+      <c r="C57" s="14">
+        <v>10</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B58" s="14">
+        <v>16</v>
+      </c>
+      <c r="C58" s="14">
+        <v>4</v>
+      </c>
+      <c r="D58" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" s="14">
+        <v>15</v>
+      </c>
+      <c r="C59" s="14">
+        <v>8</v>
+      </c>
+      <c r="D59" s="14">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="B56" s="14">
-        <v>3</v>
-      </c>
-      <c r="C56" s="14">
-        <v>2</v>
-      </c>
-      <c r="D56" s="14">
-        <v>5</v>
+      <c r="B60" s="14">
+        <v>70</v>
+      </c>
+      <c r="C60" s="14">
+        <v>30</v>
+      </c>
+      <c r="D60" s="14">
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -19974,7 +21169,7 @@
         <v>6</v>
       </c>
       <c r="B67" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
@@ -19994,7 +21189,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="14">
-        <v>2120</v>
+        <v>35258</v>
       </c>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
@@ -20030,11 +21225,11 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="14">
-        <v>2120</v>
+        <v>35258</v>
       </c>
       <c r="C78" t="str">
         <f>TEXT(A78,"#,##")</f>
-        <v>2,120</v>
+        <v>35,258</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -20071,7 +21266,7 @@
         <v>30</v>
       </c>
       <c r="B86" s="14">
-        <v>2120</v>
+        <v>5456</v>
       </c>
       <c r="D86" t="str">
         <f>A86</f>
@@ -20080,20 +21275,50 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>316</v>
+        <v>17</v>
       </c>
       <c r="B87" s="14">
-        <v>2120</v>
+        <v>3635</v>
       </c>
       <c r="D87" t="str">
         <f>A87</f>
-        <v>Grand Total</v>
+        <v>East</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D88">
+      <c r="A88" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" s="14">
+        <v>10491</v>
+      </c>
+      <c r="D88" t="str">
         <f>A88</f>
-        <v>0</v>
+        <v>North</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B89" s="14">
+        <v>7317</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B90" s="14">
+        <v>8359</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="B91" s="14">
+        <v>35258</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -20109,9 +21334,15 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
+        <v>331</v>
+      </c>
+      <c r="C98" t="s">
         <v>325</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
+        <v>332</v>
+      </c>
+      <c r="E98" t="s">
         <v>316</v>
       </c>
       <c r="G98" t="s">
@@ -20123,18 +21354,24 @@
         <v>321</v>
       </c>
       <c r="B99" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C99" s="14">
-        <v>5</v>
+        <v>66</v>
+      </c>
+      <c r="D99" s="14">
+        <v>23</v>
+      </c>
+      <c r="E99" s="14">
+        <v>100</v>
       </c>
       <c r="G99" s="11">
         <f>B99/(B99+D99)</f>
-        <v>1</v>
+        <v>0.3235294117647059</v>
       </c>
       <c r="I99" s="11">
         <f>G99</f>
-        <v>1</v>
+        <v>0.3235294117647059</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
@@ -20170,68 +21407,43 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="B107" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D107" t="str">
         <f>A107</f>
-        <v>Bluetooth Speaker</v>
+        <v>Leg Set</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B108" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D108" t="str">
         <f>A108</f>
-        <v>Cookware Set</v>
+        <v>T-Shirt</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
-        <v>238</v>
+        <v>316</v>
       </c>
       <c r="B109" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="B110" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="B111" s="14">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="B112" s="14">
-        <v>5</v>
-      </c>
       <c r="C112" s="20"/>
       <c r="D112" s="20"/>
       <c r="E112" s="23"/>
     </row>
     <row r="113" spans="1:2" ht="14.3" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="1:2" ht="14.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="10"/>
-      <c r="B114" s="14"/>
-    </row>
+    <row r="114" spans="1:2" ht="14.3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="115" spans="1:2" ht="14.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="10"/>
       <c r="B115" s="14"/>
@@ -20242,7 +21454,7 @@
     </row>
     <row r="117" spans="1:2" ht="14.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="31" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B117" s="14"/>
     </row>
@@ -20257,18 +21469,18 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="30" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B120" s="14">
-        <v>685</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="30" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B121" s="14">
-        <v>829</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -20276,27 +21488,91 @@
         <v>351</v>
       </c>
       <c r="B122" s="14">
-        <v>315</v>
+        <v>905</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="30" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B123" s="14">
-        <v>291</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="30" t="s">
+        <v>355</v>
+      </c>
+      <c r="B124" s="14">
+        <v>4940</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="B125" s="14">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="B126" s="14">
+        <v>3315</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="30" t="s">
+        <v>357</v>
+      </c>
+      <c r="B127" s="14">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="B128" s="14">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="30" t="s">
+        <v>359</v>
+      </c>
+      <c r="B129" s="14">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="B130" s="14">
+        <v>6312</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="B131" s="14">
+        <v>4467</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="30" t="s">
         <v>316</v>
       </c>
-      <c r="B124" s="14">
-        <v>2120</v>
-      </c>
-    </row>
-    <row r="133" ht="15.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="13.6" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B132" s="14">
+        <v>35258</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="15.65" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" spans="1:2" ht="13.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
@@ -20537,7 +21813,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F287202-60CB-4386-8CF0-D308258983A0}">
-  <dimension ref="A3:B9"/>
+  <dimension ref="A3:B7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.625" bestFit="1" customWidth="1"/>
@@ -20554,50 +21830,34 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B4" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="B5" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="B6" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
-        <v>137</v>
+      <c r="A7" s="10" t="s">
+        <v>316</v>
       </c>
       <c r="B7" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
-        <v>247</v>
-      </c>
-      <c r="B8" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="B9" s="14">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
